--- a/PKCS11_Requirements_Coverage.xlsx
+++ b/PKCS11_Requirements_Coverage.xlsx
@@ -834,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>248</v>
+        <v>314</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -931,11 +931,11 @@
         <v>3</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>91.9%</t>
         </is>
       </c>
     </row>
@@ -1190,11 +1190,11 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>objects</t>
+          <t>neg_scenarios</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>0</v>
@@ -1203,22 +1203,18 @@
         <v>0</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Object CRUD and search</t>
-        </is>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>parallel</t>
+          <t>objects</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>0</v>
@@ -1227,22 +1223,22 @@
         <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Multi-threaded session safety</t>
+          <t>Object CRUD and search</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>parallel</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>0</v>
@@ -1251,22 +1247,22 @@
         <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Random number generation</t>
+          <t>Multi-threaded session safety</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>req_crypto</t>
+          <t>random</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>0</v>
@@ -1275,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>REQ: Cryptographic ops (§11.8-11.15)</t>
+          <t>Random number generation</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>req_general</t>
+          <t>req_crypto</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>0</v>
@@ -1299,22 +1295,22 @@
         <v>0</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>REQ: General &amp; slot/token (§11.4-11.5)</t>
+          <t>REQ: Cryptographic ops (§11.8-11.15)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>req_objects</t>
+          <t>req_general</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>0</v>
@@ -1323,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>REQ: Object management (§11.7)</t>
+          <t>REQ: General &amp; slot/token (§11.4-11.5)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>req_session</t>
+          <t>req_objects</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>0</v>
@@ -1347,22 +1343,22 @@
         <v>0</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>REQ: Session &amp; login (§11.6)</t>
+          <t>REQ: Object management (§11.7)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>session</t>
+          <t>req_session</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>0</v>
@@ -1371,22 +1367,22 @@
         <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Session lifecycle</t>
+          <t>REQ: Session &amp; login (§11.6)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>slot_token</t>
+          <t>session</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>0</v>
@@ -1395,22 +1391,22 @@
         <v>0</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>Slot and token management</t>
+          <t>Session lifecycle</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>wrap_unwrap</t>
+          <t>slot_token</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>0</v>
@@ -1419,26 +1415,50 @@
         <v>0</v>
       </c>
       <c r="E27" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Slot and token management</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>wrap_unwrap</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Key wrap and unwrap</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>PASS – test executed and succeeded</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>FAIL – test executed and failed</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>SKIP – mechanism not supported by SoftHSM2 2.6.1</t>
         </is>
@@ -1460,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6739,6 +6759,1192 @@
           <t>Mechanism not supported by SoftHSM2 2.6.1</t>
         </is>
       </c>
+    </row>
+    <row r="157" ht="30" customHeight="1">
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="B157" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D157" s="18" t="inlineStr">
+        <is>
+          <t>Invalid session handle → CKR_SESSION_HANDLE_INVALID</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
+        <is>
+          <t>NEG-SESS-01_EncryptInit_invalid_sess
+NEG-SESS-02_DecryptInit_invalid_sess
+NEG-SESS-03_DigestInit_invalid_sess
+NEG-SESS-04_SignInit_invalid_sess
+NEG-SESS-05_VerifyInit_invalid_sess
+NEG-SESS-06_GenerateKey_invalid_sess
+NEG-SESS-07_GenerateKeyPair_invalid_sess
+NEG-SESS-08_WrapKey_invalid_sess
+NEG-SESS-09_FindObjectsInit_invalid_sess
+NEG-SESS-10_CreateObject_invalid_sess
+NEG-SESS-11_DestroyObject_invalid_sess
+NEG-SESS-12_GenerateRandom_invalid_sess
+NEG-SESS-13_Login_invalid_sess
+NEG-SESS-14_Logout_invalid_sess
+NEG-SESS-15_GetAttributeValue_invalid_sess</t>
+        </is>
+      </c>
+      <c r="F157" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G157" s="21" t="inlineStr"/>
+    </row>
+    <row r="158" ht="30" customHeight="1">
+      <c r="A158" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-02</t>
+        </is>
+      </c>
+      <c r="B158" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C158" s="23" t="inlineStr">
+        <is>
+          <t>C_EncryptInit/C_DecryptInit/C_SignInit/C_VerifyInit</t>
+        </is>
+      </c>
+      <c r="D158" s="24" t="inlineStr">
+        <is>
+          <t>Invalid key handle → CKR_KEY_HANDLE_INVALID or CKR_OBJECT_HANDLE_INVALID</t>
+        </is>
+      </c>
+      <c r="E158" s="25" t="inlineStr">
+        <is>
+          <t>NEG-KEY-01_EncryptInit_invalid_key
+NEG-KEY-02_DecryptInit_invalid_key
+NEG-KEY-03_SignInit_invalid_key
+NEG-KEY-04_VerifyInit_invalid_key</t>
+        </is>
+      </c>
+      <c r="F158" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G158" s="26" t="inlineStr"/>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-03</t>
+        </is>
+      </c>
+      <c r="B159" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>C_WrapKey</t>
+        </is>
+      </c>
+      <c r="D159" s="18" t="inlineStr">
+        <is>
+          <t>Invalid wrapping key → CKR_WRAPPING_KEY_HANDLE_INVALID</t>
+        </is>
+      </c>
+      <c r="E159" s="19" t="inlineStr">
+        <is>
+          <t>NEG-KEY-05_WrapKey_invalid_wrapping
+NEG-KEY-06_WrapKey_invalid_target</t>
+        </is>
+      </c>
+      <c r="F159" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G159" s="21" t="inlineStr"/>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-04</t>
+        </is>
+      </c>
+      <c r="B160" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C160" s="23" t="inlineStr">
+        <is>
+          <t>C_SignInit</t>
+        </is>
+      </c>
+      <c r="D160" s="24" t="inlineStr">
+        <is>
+          <t>Wrong key type → CKR_KEY_TYPE_INCONSISTENT (or deferred error)</t>
+        </is>
+      </c>
+      <c r="E160" s="25" t="inlineStr">
+        <is>
+          <t>NEG-KEY-07_Sign_wrong_key_type
+NEG-MECH-08_RSA_sign_mech_with_AES_key</t>
+        </is>
+      </c>
+      <c r="F160" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G160" s="26" t="inlineStr"/>
+    </row>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-05</t>
+        </is>
+      </c>
+      <c r="B161" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>C_EncryptInit</t>
+        </is>
+      </c>
+      <c r="D161" s="18" t="inlineStr">
+        <is>
+          <t>Wrong key type/function → CKR_KEY_FUNCTION_NOT_PERMITTED</t>
+        </is>
+      </c>
+      <c r="E161" s="19" t="inlineStr">
+        <is>
+          <t>NEG-KEY-08_Encrypt_rsa_key_for_aes</t>
+        </is>
+      </c>
+      <c r="F161" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G161" s="21" t="inlineStr"/>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-06</t>
+        </is>
+      </c>
+      <c r="B162" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C162" s="23" t="inlineStr">
+        <is>
+          <t>C_EncryptInit</t>
+        </is>
+      </c>
+      <c r="D162" s="24" t="inlineStr">
+        <is>
+          <t>NULL IV for CBC → CKR_MECHANISM_PARAM_INVALID or CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E162" s="25" t="inlineStr">
+        <is>
+          <t>NEG-MECH-01_CBC_null_iv
+NEG-MECH-02_CBC_wrong_iv_len
+NEG-MECH-03_CBC_zero_iv_len</t>
+        </is>
+      </c>
+      <c r="F162" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G162" s="26" t="inlineStr"/>
+    </row>
+    <row r="163" ht="30" customHeight="1">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-07</t>
+        </is>
+      </c>
+      <c r="B163" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C163" s="17" t="inlineStr">
+        <is>
+          <t>C_EncryptInit</t>
+        </is>
+      </c>
+      <c r="D163" s="18" t="inlineStr">
+        <is>
+          <t>NULL GCM params → error</t>
+        </is>
+      </c>
+      <c r="E163" s="19" t="inlineStr">
+        <is>
+          <t>NEG-MECH-04_GCM_null_params</t>
+        </is>
+      </c>
+      <c r="F163" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G163" s="21" t="inlineStr"/>
+    </row>
+    <row r="164" ht="30" customHeight="1">
+      <c r="A164" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-08</t>
+        </is>
+      </c>
+      <c r="B164" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C164" s="23" t="inlineStr">
+        <is>
+          <t>C_Encrypt</t>
+        </is>
+      </c>
+      <c r="D164" s="24" t="inlineStr">
+        <is>
+          <t>Data too long for mechanism → CKR_DATA_LEN_RANGE</t>
+        </is>
+      </c>
+      <c r="E164" s="25" t="inlineStr">
+        <is>
+          <t>NEG-MECH-05_RSA_data_too_long</t>
+        </is>
+      </c>
+      <c r="F164" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G164" s="26" t="inlineStr"/>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-09</t>
+        </is>
+      </c>
+      <c r="B165" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>C_Decrypt</t>
+        </is>
+      </c>
+      <c r="D165" s="18" t="inlineStr">
+        <is>
+          <t>Non-block-aligned ciphertext → CKR_ENCRYPTED_DATA_LEN_RANGE</t>
+        </is>
+      </c>
+      <c r="E165" s="19" t="inlineStr">
+        <is>
+          <t>NEG-MECH-06_CBC_unaligned_decrypt</t>
+        </is>
+      </c>
+      <c r="F165" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G165" s="21" t="inlineStr"/>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-10</t>
+        </is>
+      </c>
+      <c r="B166" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C166" s="23" t="inlineStr">
+        <is>
+          <t>C_Decrypt</t>
+        </is>
+      </c>
+      <c r="D166" s="24" t="inlineStr">
+        <is>
+          <t>Invalid padding → CKR_ENCRYPTED_DATA_INVALID</t>
+        </is>
+      </c>
+      <c r="E166" s="25" t="inlineStr">
+        <is>
+          <t>NEG-MECH-07_CBCPAD_bad_padding</t>
+        </is>
+      </c>
+      <c r="F166" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G166" s="26" t="inlineStr"/>
+    </row>
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-11</t>
+        </is>
+      </c>
+      <c r="B167" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C167" s="17" t="inlineStr">
+        <is>
+          <t>C_Encrypt/C_Decrypt</t>
+        </is>
+      </c>
+      <c r="D167" s="18" t="inlineStr">
+        <is>
+          <t>NULL input data non-zero length → CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E167" s="19" t="inlineStr">
+        <is>
+          <t>NEG-DATA-01_Encrypt_null_input
+NEG-DATA-02_Decrypt_null_input</t>
+        </is>
+      </c>
+      <c r="F167" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G167" s="21" t="inlineStr"/>
+    </row>
+    <row r="168" ht="30" customHeight="1">
+      <c r="A168" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-12</t>
+        </is>
+      </c>
+      <c r="B168" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C168" s="23" t="inlineStr">
+        <is>
+          <t>C_DigestUpdate</t>
+        </is>
+      </c>
+      <c r="D168" s="24" t="inlineStr">
+        <is>
+          <t>NULL input → CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E168" s="25" t="inlineStr">
+        <is>
+          <t>NEG-DATA-03_Digest_null_input</t>
+        </is>
+      </c>
+      <c r="F168" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G168" s="26" t="inlineStr"/>
+    </row>
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-13</t>
+        </is>
+      </c>
+      <c r="B169" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
+        <is>
+          <t>C_Sign/C_Verify</t>
+        </is>
+      </c>
+      <c r="D169" s="18" t="inlineStr">
+        <is>
+          <t>NULL input/sig → CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E169" s="19" t="inlineStr">
+        <is>
+          <t>NEG-DATA-04_Sign_null_input
+NEG-DATA-05_Verify_null_input
+NEG-DATA-06_Verify_null_sig</t>
+        </is>
+      </c>
+      <c r="F169" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G169" s="21" t="inlineStr"/>
+    </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-14</t>
+        </is>
+      </c>
+      <c r="B170" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C170" s="23" t="inlineStr">
+        <is>
+          <t>C_Encrypt</t>
+        </is>
+      </c>
+      <c r="D170" s="24" t="inlineStr">
+        <is>
+          <t>NULL output length → CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E170" s="25" t="inlineStr">
+        <is>
+          <t>NEG-DATA-07_Encrypt_null_outlen</t>
+        </is>
+      </c>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G170" s="26" t="inlineStr"/>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-15</t>
+        </is>
+      </c>
+      <c r="B171" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
+        <is>
+          <t>C_EncryptFinal/C_DecryptFinal/C_DigestFinal/C_SignFinal</t>
+        </is>
+      </c>
+      <c r="D171" s="18" t="inlineStr">
+        <is>
+          <t>Buffer too small → CKR_BUFFER_TOO_SMALL</t>
+        </is>
+      </c>
+      <c r="E171" s="19" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-01_EncryptFinal_too_small
+NEG-SEQ-02_DecryptFinal_too_small
+NEG-SEQ-03_DigestFinal_too_small
+NEG-SEQ-04_SignFinal_too_small</t>
+        </is>
+      </c>
+      <c r="F171" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G171" s="21" t="inlineStr"/>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-16</t>
+        </is>
+      </c>
+      <c r="B172" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C172" s="23" t="inlineStr">
+        <is>
+          <t>C_Encrypt/C_EncryptUpdate</t>
+        </is>
+      </c>
+      <c r="D172" s="24" t="inlineStr">
+        <is>
+          <t>Mixing single/multi-part ops</t>
+        </is>
+      </c>
+      <c r="E172" s="25" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-05_Encrypt_after_EncryptUpdate
+NEG-SEQ-06_EncryptUpdate_after_Encrypt</t>
+        </is>
+      </c>
+      <c r="F172" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G172" s="26" t="inlineStr"/>
+    </row>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-17</t>
+        </is>
+      </c>
+      <c r="B173" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C173" s="17" t="inlineStr">
+        <is>
+          <t>C_SignFinal/C_VerifyFinal</t>
+        </is>
+      </c>
+      <c r="D173" s="18" t="inlineStr">
+        <is>
+          <t>Final without Update (empty message or error)</t>
+        </is>
+      </c>
+      <c r="E173" s="19" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-07_SignFinal_no_update
+NEG-SEQ-08_VerifyFinal_no_update</t>
+        </is>
+      </c>
+      <c r="F173" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G173" s="21" t="inlineStr"/>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-18</t>
+        </is>
+      </c>
+      <c r="B174" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C174" s="23" t="inlineStr">
+        <is>
+          <t>C_DestroyObject</t>
+        </is>
+      </c>
+      <c r="D174" s="24" t="inlineStr">
+        <is>
+          <t>RO session cannot destroy token objects → CKR_SESSION_READ_ONLY</t>
+        </is>
+      </c>
+      <c r="E174" s="25" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-01_Destroy_on_ro_session</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G174" s="26" t="inlineStr"/>
+    </row>
+    <row r="175" ht="30" customHeight="1">
+      <c r="A175" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-19</t>
+        </is>
+      </c>
+      <c r="B175" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
+        <is>
+          <t>C_CopyObject</t>
+        </is>
+      </c>
+      <c r="D175" s="18" t="inlineStr">
+        <is>
+          <t>Invalid source handle → CKR_OBJECT_HANDLE_INVALID</t>
+        </is>
+      </c>
+      <c r="E175" s="19" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-02_CopyObject_invalid_src</t>
+        </is>
+      </c>
+      <c r="F175" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G175" s="21" t="inlineStr"/>
+    </row>
+    <row r="176" ht="30" customHeight="1">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-20</t>
+        </is>
+      </c>
+      <c r="B176" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C176" s="23" t="inlineStr">
+        <is>
+          <t>C_DestroyObject</t>
+        </is>
+      </c>
+      <c r="D176" s="24" t="inlineStr">
+        <is>
+          <t>CKA_DESTROYABLE=FALSE → CKR_ACTION_PROHIBITED</t>
+        </is>
+      </c>
+      <c r="E176" s="25" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-03_Non_destroyable_object</t>
+        </is>
+      </c>
+      <c r="F176" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G176" s="26" t="inlineStr"/>
+    </row>
+    <row r="177" ht="30" customHeight="1">
+      <c r="A177" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-21</t>
+        </is>
+      </c>
+      <c r="B177" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C177" s="17" t="inlineStr">
+        <is>
+          <t>C_SetAttributeValue/C_GetAttributeValue</t>
+        </is>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>NULL template non-zero count → CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-04_SetAttr_null_template
+NEG-OBJ-05_GetAttr_null_template</t>
+        </is>
+      </c>
+      <c r="F177" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G177" s="21" t="inlineStr"/>
+    </row>
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-22</t>
+        </is>
+      </c>
+      <c r="B178" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C178" s="23" t="inlineStr">
+        <is>
+          <t>C_FindObjectsInit</t>
+        </is>
+      </c>
+      <c r="D178" s="24" t="inlineStr">
+        <is>
+          <t>NULL template non-zero count → CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E178" s="25" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-06_FindInit_null_tmpl_nonzero</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G178" s="26" t="inlineStr"/>
+    </row>
+    <row r="179" ht="30" customHeight="1">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-23</t>
+        </is>
+      </c>
+      <c r="B179" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C179" s="17" t="inlineStr">
+        <is>
+          <t>C_CreateObject</t>
+        </is>
+      </c>
+      <c r="D179" s="18" t="inlineStr">
+        <is>
+          <t>Inconsistent template → CKR_TEMPLATE_INCONSISTENT</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-07_CreateObject_inconsistent_tmpl</t>
+        </is>
+      </c>
+      <c r="F179" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G179" s="21" t="inlineStr"/>
+    </row>
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-24</t>
+        </is>
+      </c>
+      <c r="B180" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C180" s="23" t="inlineStr">
+        <is>
+          <t>C_WrapKey</t>
+        </is>
+      </c>
+      <c r="D180" s="24" t="inlineStr">
+        <is>
+          <t>Invalid/unsupported wrap mechanism → error</t>
+        </is>
+      </c>
+      <c r="E180" s="25" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-01_WrapKey_invalid_mechanism</t>
+        </is>
+      </c>
+      <c r="F180" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G180" s="26" t="inlineStr"/>
+    </row>
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-25</t>
+        </is>
+      </c>
+      <c r="B181" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>C_UnwrapKey</t>
+        </is>
+      </c>
+      <c r="D181" s="18" t="inlineStr">
+        <is>
+          <t>Corrupt wrapped data → CKR_WRAPPED_KEY_INVALID</t>
+        </is>
+      </c>
+      <c r="E181" s="19" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-02_UnwrapKey_corrupt_blob</t>
+        </is>
+      </c>
+      <c r="F181" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G181" s="21" t="inlineStr"/>
+    </row>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-26</t>
+        </is>
+      </c>
+      <c r="B182" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C182" s="23" t="inlineStr">
+        <is>
+          <t>C_UnwrapKey</t>
+        </is>
+      </c>
+      <c r="D182" s="24" t="inlineStr">
+        <is>
+          <t>NULL wrapped data → CKR_ARGUMENTS_BAD</t>
+        </is>
+      </c>
+      <c r="E182" s="25" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-03_UnwrapKey_null_data</t>
+        </is>
+      </c>
+      <c r="F182" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G182" s="26" t="inlineStr"/>
+    </row>
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-27</t>
+        </is>
+      </c>
+      <c r="B183" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C183" s="17" t="inlineStr">
+        <is>
+          <t>C_WrapKey</t>
+        </is>
+      </c>
+      <c r="D183" s="18" t="inlineStr">
+        <is>
+          <t>Key without CKA_WRAP → CKR_KEY_NOT_WRAPPABLE</t>
+        </is>
+      </c>
+      <c r="E183" s="19" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-04_WrapKey_no_wrap_flag</t>
+        </is>
+      </c>
+      <c r="F183" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G183" s="21" t="inlineStr"/>
+    </row>
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-28</t>
+        </is>
+      </c>
+      <c r="B184" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C184" s="23" t="inlineStr">
+        <is>
+          <t>C_GenerateKey</t>
+        </is>
+      </c>
+      <c r="D184" s="24" t="inlineStr">
+        <is>
+          <t>Invalid key length → CKR_KEY_SIZE_RANGE</t>
+        </is>
+      </c>
+      <c r="E184" s="25" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-01_AES_invalid_length</t>
+        </is>
+      </c>
+      <c r="F184" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G184" s="26" t="inlineStr"/>
+    </row>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-29</t>
+        </is>
+      </c>
+      <c r="B185" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C185" s="17" t="inlineStr">
+        <is>
+          <t>C_GenerateKey</t>
+        </is>
+      </c>
+      <c r="D185" s="18" t="inlineStr">
+        <is>
+          <t>Missing VALUE_LEN → CKR_TEMPLATE_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="E185" s="19" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-02_AES_missing_value_len</t>
+        </is>
+      </c>
+      <c r="F185" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G185" s="21" t="inlineStr"/>
+    </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-30</t>
+        </is>
+      </c>
+      <c r="B186" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C186" s="23" t="inlineStr">
+        <is>
+          <t>C_GenerateKeyPair</t>
+        </is>
+      </c>
+      <c r="D186" s="24" t="inlineStr">
+        <is>
+          <t>Invalid RSA modulus bits → error</t>
+        </is>
+      </c>
+      <c r="E186" s="25" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-03_RSA_zero_bits</t>
+        </is>
+      </c>
+      <c r="F186" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G186" s="26" t="inlineStr"/>
+    </row>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-31</t>
+        </is>
+      </c>
+      <c r="B187" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
+        <is>
+          <t>C_GenerateKey</t>
+        </is>
+      </c>
+      <c r="D187" s="18" t="inlineStr">
+        <is>
+          <t>CKA_TOKEN=TRUE on RO session → CKR_SESSION_READ_ONLY</t>
+        </is>
+      </c>
+      <c r="E187" s="19" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-04_GenerateKey_on_ro_session</t>
+        </is>
+      </c>
+      <c r="F187" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G187" s="21" t="inlineStr"/>
+    </row>
+    <row r="188" ht="30" customHeight="1">
+      <c r="A188" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-32</t>
+        </is>
+      </c>
+      <c r="B188" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C188" s="23" t="inlineStr">
+        <is>
+          <t>C_DecryptInit/C_SignInit</t>
+        </is>
+      </c>
+      <c r="D188" s="24" t="inlineStr">
+        <is>
+          <t>Second init while op active → CKR_OPERATION_ACTIVE</t>
+        </is>
+      </c>
+      <c r="E188" s="25" t="inlineStr">
+        <is>
+          <t>NEG-ENC-01_DecryptInit_while_Encrypt_active
+NEG-ENC-02_SignInit_while_Digest_active</t>
+        </is>
+      </c>
+      <c r="F188" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G188" s="26" t="inlineStr"/>
+    </row>
+    <row r="189" ht="30" customHeight="1">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-33</t>
+        </is>
+      </c>
+      <c r="B189" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C189" s="17" t="inlineStr">
+        <is>
+          <t>C_Decrypt</t>
+        </is>
+      </c>
+      <c r="D189" s="18" t="inlineStr">
+        <is>
+          <t>GCM authentication tag tampered → CKR_ENCRYPTED_DATA_INVALID</t>
+        </is>
+      </c>
+      <c r="E189" s="19" t="inlineStr">
+        <is>
+          <t>NEG-ENC-03_GCM_tampered_tag</t>
+        </is>
+      </c>
+      <c r="F189" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G189" s="21" t="inlineStr"/>
+    </row>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="22" t="inlineStr">
+        <is>
+          <t>REQ-NEG-34</t>
+        </is>
+      </c>
+      <c r="B190" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C190" s="23" t="inlineStr">
+        <is>
+          <t>C_Decrypt</t>
+        </is>
+      </c>
+      <c r="D190" s="24" t="inlineStr">
+        <is>
+          <t>Random RSA ciphertext: implementation-defined behavior</t>
+        </is>
+      </c>
+      <c r="E190" s="25" t="inlineStr">
+        <is>
+          <t>NEG-ENC-04_RSA_random_ciphertext</t>
+        </is>
+      </c>
+      <c r="F190" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G190" s="26" t="inlineStr"/>
+    </row>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>REQ-NEG-35</t>
+        </is>
+      </c>
+      <c r="B191" s="38" t="inlineStr">
+        <is>
+          <t>§11.x</t>
+        </is>
+      </c>
+      <c r="C191" s="17" t="inlineStr">
+        <is>
+          <t>C_Decrypt</t>
+        </is>
+      </c>
+      <c r="D191" s="18" t="inlineStr">
+        <is>
+          <t>Buffer too small → CKR_BUFFER_TOO_SMALL</t>
+        </is>
+      </c>
+      <c r="E191" s="19" t="inlineStr">
+        <is>
+          <t>NEG-ENC-05_Decrypt_buffer_too_small</t>
+        </is>
+      </c>
+      <c r="F191" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G191" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6755,7 +7961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E257"/>
+  <dimension ref="A1:E323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12691,6 +13897,1524 @@
         </is>
       </c>
       <c r="E257" s="45" t="inlineStr"/>
+    </row>
+    <row r="258" ht="16" customHeight="1">
+      <c r="A258" s="41" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B258" s="24" t="inlineStr">
+        <is>
+          <t>NEG-SESS-01_EncryptInit_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C258" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D258" s="25" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E258" s="26" t="inlineStr"/>
+    </row>
+    <row r="259" ht="16" customHeight="1">
+      <c r="A259" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B259" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SESS-02_DecryptInit_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C259" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D259" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E259" s="45" t="inlineStr"/>
+    </row>
+    <row r="260" ht="16" customHeight="1">
+      <c r="A260" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B260" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SESS-03_DigestInit_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C260" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D260" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E260" s="21" t="inlineStr"/>
+    </row>
+    <row r="261" ht="16" customHeight="1">
+      <c r="A261" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B261" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SESS-04_SignInit_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C261" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D261" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E261" s="45" t="inlineStr"/>
+    </row>
+    <row r="262" ht="16" customHeight="1">
+      <c r="A262" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B262" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SESS-05_VerifyInit_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C262" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D262" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E262" s="21" t="inlineStr"/>
+    </row>
+    <row r="263" ht="16" customHeight="1">
+      <c r="A263" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B263" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SESS-06_GenerateKey_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C263" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D263" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E263" s="45" t="inlineStr"/>
+    </row>
+    <row r="264" ht="16" customHeight="1">
+      <c r="A264" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B264" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SESS-07_GenerateKeyPair_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C264" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D264" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E264" s="21" t="inlineStr"/>
+    </row>
+    <row r="265" ht="16" customHeight="1">
+      <c r="A265" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B265" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SESS-08_WrapKey_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C265" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D265" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E265" s="45" t="inlineStr"/>
+    </row>
+    <row r="266" ht="16" customHeight="1">
+      <c r="A266" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B266" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SESS-09_FindObjectsInit_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C266" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D266" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E266" s="21" t="inlineStr"/>
+    </row>
+    <row r="267" ht="16" customHeight="1">
+      <c r="A267" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B267" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SESS-10_CreateObject_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C267" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D267" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E267" s="45" t="inlineStr"/>
+    </row>
+    <row r="268" ht="16" customHeight="1">
+      <c r="A268" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B268" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SESS-11_DestroyObject_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C268" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D268" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E268" s="21" t="inlineStr"/>
+    </row>
+    <row r="269" ht="16" customHeight="1">
+      <c r="A269" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B269" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SESS-12_GenerateRandom_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C269" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D269" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E269" s="45" t="inlineStr"/>
+    </row>
+    <row r="270" ht="16" customHeight="1">
+      <c r="A270" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B270" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SESS-13_Login_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C270" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D270" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E270" s="21" t="inlineStr"/>
+    </row>
+    <row r="271" ht="16" customHeight="1">
+      <c r="A271" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B271" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SESS-14_Logout_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C271" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D271" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E271" s="45" t="inlineStr"/>
+    </row>
+    <row r="272" ht="16" customHeight="1">
+      <c r="A272" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B272" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SESS-15_GetAttributeValue_invalid_sess</t>
+        </is>
+      </c>
+      <c r="C272" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D272" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-01</t>
+        </is>
+      </c>
+      <c r="E272" s="21" t="inlineStr"/>
+    </row>
+    <row r="273" ht="16" customHeight="1">
+      <c r="A273" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B273" s="43" t="inlineStr">
+        <is>
+          <t>NEG-KEY-01_EncryptInit_invalid_key</t>
+        </is>
+      </c>
+      <c r="C273" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D273" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-02</t>
+        </is>
+      </c>
+      <c r="E273" s="45" t="inlineStr"/>
+    </row>
+    <row r="274" ht="16" customHeight="1">
+      <c r="A274" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B274" s="18" t="inlineStr">
+        <is>
+          <t>NEG-KEY-02_DecryptInit_invalid_key</t>
+        </is>
+      </c>
+      <c r="C274" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D274" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-02</t>
+        </is>
+      </c>
+      <c r="E274" s="21" t="inlineStr"/>
+    </row>
+    <row r="275" ht="16" customHeight="1">
+      <c r="A275" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B275" s="43" t="inlineStr">
+        <is>
+          <t>NEG-KEY-03_SignInit_invalid_key</t>
+        </is>
+      </c>
+      <c r="C275" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D275" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-02</t>
+        </is>
+      </c>
+      <c r="E275" s="45" t="inlineStr"/>
+    </row>
+    <row r="276" ht="16" customHeight="1">
+      <c r="A276" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B276" s="18" t="inlineStr">
+        <is>
+          <t>NEG-KEY-04_VerifyInit_invalid_key</t>
+        </is>
+      </c>
+      <c r="C276" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D276" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-02</t>
+        </is>
+      </c>
+      <c r="E276" s="21" t="inlineStr"/>
+    </row>
+    <row r="277" ht="16" customHeight="1">
+      <c r="A277" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B277" s="43" t="inlineStr">
+        <is>
+          <t>NEG-KEY-05_WrapKey_invalid_wrapping</t>
+        </is>
+      </c>
+      <c r="C277" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D277" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-03</t>
+        </is>
+      </c>
+      <c r="E277" s="45" t="inlineStr"/>
+    </row>
+    <row r="278" ht="16" customHeight="1">
+      <c r="A278" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B278" s="18" t="inlineStr">
+        <is>
+          <t>NEG-KEY-06_WrapKey_invalid_target</t>
+        </is>
+      </c>
+      <c r="C278" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D278" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-03</t>
+        </is>
+      </c>
+      <c r="E278" s="21" t="inlineStr"/>
+    </row>
+    <row r="279" ht="16" customHeight="1">
+      <c r="A279" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B279" s="43" t="inlineStr">
+        <is>
+          <t>NEG-KEY-07_Sign_wrong_key_type</t>
+        </is>
+      </c>
+      <c r="C279" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D279" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-04</t>
+        </is>
+      </c>
+      <c r="E279" s="45" t="inlineStr"/>
+    </row>
+    <row r="280" ht="16" customHeight="1">
+      <c r="A280" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B280" s="18" t="inlineStr">
+        <is>
+          <t>NEG-KEY-08_Encrypt_rsa_key_for_aes</t>
+        </is>
+      </c>
+      <c r="C280" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D280" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-05</t>
+        </is>
+      </c>
+      <c r="E280" s="21" t="inlineStr"/>
+    </row>
+    <row r="281" ht="16" customHeight="1">
+      <c r="A281" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B281" s="43" t="inlineStr">
+        <is>
+          <t>NEG-MECH-01_CBC_null_iv</t>
+        </is>
+      </c>
+      <c r="C281" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D281" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-06</t>
+        </is>
+      </c>
+      <c r="E281" s="45" t="inlineStr"/>
+    </row>
+    <row r="282" ht="16" customHeight="1">
+      <c r="A282" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B282" s="18" t="inlineStr">
+        <is>
+          <t>NEG-MECH-02_CBC_wrong_iv_len</t>
+        </is>
+      </c>
+      <c r="C282" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D282" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-06</t>
+        </is>
+      </c>
+      <c r="E282" s="21" t="inlineStr"/>
+    </row>
+    <row r="283" ht="16" customHeight="1">
+      <c r="A283" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B283" s="43" t="inlineStr">
+        <is>
+          <t>NEG-MECH-03_CBC_zero_iv_len</t>
+        </is>
+      </c>
+      <c r="C283" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D283" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-06</t>
+        </is>
+      </c>
+      <c r="E283" s="45" t="inlineStr"/>
+    </row>
+    <row r="284" ht="16" customHeight="1">
+      <c r="A284" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B284" s="18" t="inlineStr">
+        <is>
+          <t>NEG-MECH-04_GCM_null_params</t>
+        </is>
+      </c>
+      <c r="C284" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D284" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-07</t>
+        </is>
+      </c>
+      <c r="E284" s="21" t="inlineStr"/>
+    </row>
+    <row r="285" ht="16" customHeight="1">
+      <c r="A285" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B285" s="43" t="inlineStr">
+        <is>
+          <t>NEG-MECH-05_RSA_data_too_long</t>
+        </is>
+      </c>
+      <c r="C285" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D285" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-08</t>
+        </is>
+      </c>
+      <c r="E285" s="45" t="inlineStr"/>
+    </row>
+    <row r="286" ht="16" customHeight="1">
+      <c r="A286" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B286" s="18" t="inlineStr">
+        <is>
+          <t>NEG-MECH-06_CBC_unaligned_decrypt</t>
+        </is>
+      </c>
+      <c r="C286" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D286" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-09</t>
+        </is>
+      </c>
+      <c r="E286" s="21" t="inlineStr"/>
+    </row>
+    <row r="287" ht="16" customHeight="1">
+      <c r="A287" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B287" s="43" t="inlineStr">
+        <is>
+          <t>NEG-MECH-07_CBCPAD_bad_padding</t>
+        </is>
+      </c>
+      <c r="C287" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D287" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-10</t>
+        </is>
+      </c>
+      <c r="E287" s="45" t="inlineStr"/>
+    </row>
+    <row r="288" ht="16" customHeight="1">
+      <c r="A288" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B288" s="18" t="inlineStr">
+        <is>
+          <t>NEG-MECH-08_RSA_sign_mech_with_AES_key</t>
+        </is>
+      </c>
+      <c r="C288" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D288" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-04</t>
+        </is>
+      </c>
+      <c r="E288" s="21" t="inlineStr"/>
+    </row>
+    <row r="289" ht="16" customHeight="1">
+      <c r="A289" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B289" s="43" t="inlineStr">
+        <is>
+          <t>NEG-DATA-01_Encrypt_null_input</t>
+        </is>
+      </c>
+      <c r="C289" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D289" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-11</t>
+        </is>
+      </c>
+      <c r="E289" s="45" t="inlineStr"/>
+    </row>
+    <row r="290" ht="16" customHeight="1">
+      <c r="A290" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B290" s="18" t="inlineStr">
+        <is>
+          <t>NEG-DATA-02_Decrypt_null_input</t>
+        </is>
+      </c>
+      <c r="C290" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D290" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-11</t>
+        </is>
+      </c>
+      <c r="E290" s="21" t="inlineStr"/>
+    </row>
+    <row r="291" ht="16" customHeight="1">
+      <c r="A291" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B291" s="43" t="inlineStr">
+        <is>
+          <t>NEG-DATA-03_Digest_null_input</t>
+        </is>
+      </c>
+      <c r="C291" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D291" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-12</t>
+        </is>
+      </c>
+      <c r="E291" s="45" t="inlineStr"/>
+    </row>
+    <row r="292" ht="16" customHeight="1">
+      <c r="A292" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B292" s="18" t="inlineStr">
+        <is>
+          <t>NEG-DATA-04_Sign_null_input</t>
+        </is>
+      </c>
+      <c r="C292" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D292" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-13</t>
+        </is>
+      </c>
+      <c r="E292" s="21" t="inlineStr"/>
+    </row>
+    <row r="293" ht="16" customHeight="1">
+      <c r="A293" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B293" s="43" t="inlineStr">
+        <is>
+          <t>NEG-DATA-05_Verify_null_input</t>
+        </is>
+      </c>
+      <c r="C293" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D293" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-13</t>
+        </is>
+      </c>
+      <c r="E293" s="45" t="inlineStr"/>
+    </row>
+    <row r="294" ht="16" customHeight="1">
+      <c r="A294" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B294" s="18" t="inlineStr">
+        <is>
+          <t>NEG-DATA-06_Verify_null_sig</t>
+        </is>
+      </c>
+      <c r="C294" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D294" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-13</t>
+        </is>
+      </c>
+      <c r="E294" s="21" t="inlineStr"/>
+    </row>
+    <row r="295" ht="16" customHeight="1">
+      <c r="A295" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B295" s="43" t="inlineStr">
+        <is>
+          <t>NEG-DATA-07_Encrypt_null_outlen</t>
+        </is>
+      </c>
+      <c r="C295" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D295" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-14</t>
+        </is>
+      </c>
+      <c r="E295" s="45" t="inlineStr"/>
+    </row>
+    <row r="296" ht="16" customHeight="1">
+      <c r="A296" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B296" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-01_EncryptFinal_too_small</t>
+        </is>
+      </c>
+      <c r="C296" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D296" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-15</t>
+        </is>
+      </c>
+      <c r="E296" s="21" t="inlineStr"/>
+    </row>
+    <row r="297" ht="16" customHeight="1">
+      <c r="A297" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B297" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-02_DecryptFinal_too_small</t>
+        </is>
+      </c>
+      <c r="C297" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D297" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-15</t>
+        </is>
+      </c>
+      <c r="E297" s="45" t="inlineStr"/>
+    </row>
+    <row r="298" ht="16" customHeight="1">
+      <c r="A298" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B298" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-03_DigestFinal_too_small</t>
+        </is>
+      </c>
+      <c r="C298" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D298" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-15</t>
+        </is>
+      </c>
+      <c r="E298" s="21" t="inlineStr"/>
+    </row>
+    <row r="299" ht="16" customHeight="1">
+      <c r="A299" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B299" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-04_SignFinal_too_small</t>
+        </is>
+      </c>
+      <c r="C299" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D299" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-15</t>
+        </is>
+      </c>
+      <c r="E299" s="45" t="inlineStr"/>
+    </row>
+    <row r="300" ht="16" customHeight="1">
+      <c r="A300" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B300" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-05_Encrypt_after_EncryptUpdate</t>
+        </is>
+      </c>
+      <c r="C300" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D300" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-16</t>
+        </is>
+      </c>
+      <c r="E300" s="21" t="inlineStr"/>
+    </row>
+    <row r="301" ht="16" customHeight="1">
+      <c r="A301" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B301" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-06_EncryptUpdate_after_Encrypt</t>
+        </is>
+      </c>
+      <c r="C301" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D301" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-16</t>
+        </is>
+      </c>
+      <c r="E301" s="45" t="inlineStr"/>
+    </row>
+    <row r="302" ht="16" customHeight="1">
+      <c r="A302" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B302" s="18" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-07_SignFinal_no_update</t>
+        </is>
+      </c>
+      <c r="C302" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D302" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-17</t>
+        </is>
+      </c>
+      <c r="E302" s="21" t="inlineStr"/>
+    </row>
+    <row r="303" ht="16" customHeight="1">
+      <c r="A303" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B303" s="43" t="inlineStr">
+        <is>
+          <t>NEG-SEQ-08_VerifyFinal_no_update</t>
+        </is>
+      </c>
+      <c r="C303" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D303" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-17</t>
+        </is>
+      </c>
+      <c r="E303" s="45" t="inlineStr"/>
+    </row>
+    <row r="304" ht="16" customHeight="1">
+      <c r="A304" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B304" s="18" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-01_Destroy_on_ro_session</t>
+        </is>
+      </c>
+      <c r="C304" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D304" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-18</t>
+        </is>
+      </c>
+      <c r="E304" s="21" t="inlineStr"/>
+    </row>
+    <row r="305" ht="16" customHeight="1">
+      <c r="A305" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B305" s="43" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-02_CopyObject_invalid_src</t>
+        </is>
+      </c>
+      <c r="C305" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D305" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-19</t>
+        </is>
+      </c>
+      <c r="E305" s="45" t="inlineStr"/>
+    </row>
+    <row r="306" ht="16" customHeight="1">
+      <c r="A306" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B306" s="18" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-03_Non_destroyable_object</t>
+        </is>
+      </c>
+      <c r="C306" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D306" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-20</t>
+        </is>
+      </c>
+      <c r="E306" s="21" t="inlineStr"/>
+    </row>
+    <row r="307" ht="16" customHeight="1">
+      <c r="A307" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B307" s="43" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-04_SetAttr_null_template</t>
+        </is>
+      </c>
+      <c r="C307" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D307" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-21</t>
+        </is>
+      </c>
+      <c r="E307" s="45" t="inlineStr"/>
+    </row>
+    <row r="308" ht="16" customHeight="1">
+      <c r="A308" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B308" s="18" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-05_GetAttr_null_template</t>
+        </is>
+      </c>
+      <c r="C308" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D308" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-21</t>
+        </is>
+      </c>
+      <c r="E308" s="21" t="inlineStr"/>
+    </row>
+    <row r="309" ht="16" customHeight="1">
+      <c r="A309" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B309" s="43" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-06_FindInit_null_tmpl_nonzero</t>
+        </is>
+      </c>
+      <c r="C309" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D309" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-22</t>
+        </is>
+      </c>
+      <c r="E309" s="45" t="inlineStr"/>
+    </row>
+    <row r="310" ht="16" customHeight="1">
+      <c r="A310" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B310" s="18" t="inlineStr">
+        <is>
+          <t>NEG-OBJ-07_CreateObject_inconsistent_tmpl</t>
+        </is>
+      </c>
+      <c r="C310" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D310" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-23</t>
+        </is>
+      </c>
+      <c r="E310" s="21" t="inlineStr"/>
+    </row>
+    <row r="311" ht="16" customHeight="1">
+      <c r="A311" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B311" s="43" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-01_WrapKey_invalid_mechanism</t>
+        </is>
+      </c>
+      <c r="C311" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D311" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-24</t>
+        </is>
+      </c>
+      <c r="E311" s="45" t="inlineStr"/>
+    </row>
+    <row r="312" ht="16" customHeight="1">
+      <c r="A312" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B312" s="18" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-02_UnwrapKey_corrupt_blob</t>
+        </is>
+      </c>
+      <c r="C312" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D312" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-25</t>
+        </is>
+      </c>
+      <c r="E312" s="21" t="inlineStr"/>
+    </row>
+    <row r="313" ht="16" customHeight="1">
+      <c r="A313" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B313" s="43" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-03_UnwrapKey_null_data</t>
+        </is>
+      </c>
+      <c r="C313" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D313" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-26</t>
+        </is>
+      </c>
+      <c r="E313" s="45" t="inlineStr"/>
+    </row>
+    <row r="314" ht="16" customHeight="1">
+      <c r="A314" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B314" s="18" t="inlineStr">
+        <is>
+          <t>NEG-WRAP-04_WrapKey_no_wrap_flag</t>
+        </is>
+      </c>
+      <c r="C314" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D314" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-27</t>
+        </is>
+      </c>
+      <c r="E314" s="21" t="inlineStr"/>
+    </row>
+    <row r="315" ht="16" customHeight="1">
+      <c r="A315" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B315" s="43" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-01_AES_invalid_length</t>
+        </is>
+      </c>
+      <c r="C315" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D315" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-28</t>
+        </is>
+      </c>
+      <c r="E315" s="45" t="inlineStr"/>
+    </row>
+    <row r="316" ht="16" customHeight="1">
+      <c r="A316" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B316" s="18" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-02_AES_missing_value_len</t>
+        </is>
+      </c>
+      <c r="C316" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D316" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-29</t>
+        </is>
+      </c>
+      <c r="E316" s="21" t="inlineStr"/>
+    </row>
+    <row r="317" ht="16" customHeight="1">
+      <c r="A317" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B317" s="43" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-03_RSA_zero_bits</t>
+        </is>
+      </c>
+      <c r="C317" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D317" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-30</t>
+        </is>
+      </c>
+      <c r="E317" s="45" t="inlineStr"/>
+    </row>
+    <row r="318" ht="16" customHeight="1">
+      <c r="A318" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B318" s="18" t="inlineStr">
+        <is>
+          <t>NEG-KGEN-04_GenerateKey_on_ro_session</t>
+        </is>
+      </c>
+      <c r="C318" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D318" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-31</t>
+        </is>
+      </c>
+      <c r="E318" s="21" t="inlineStr"/>
+    </row>
+    <row r="319" ht="16" customHeight="1">
+      <c r="A319" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B319" s="43" t="inlineStr">
+        <is>
+          <t>NEG-ENC-01_DecryptInit_while_Encrypt_active</t>
+        </is>
+      </c>
+      <c r="C319" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D319" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-32</t>
+        </is>
+      </c>
+      <c r="E319" s="45" t="inlineStr"/>
+    </row>
+    <row r="320" ht="16" customHeight="1">
+      <c r="A320" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B320" s="18" t="inlineStr">
+        <is>
+          <t>NEG-ENC-02_SignInit_while_Digest_active</t>
+        </is>
+      </c>
+      <c r="C320" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D320" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-32</t>
+        </is>
+      </c>
+      <c r="E320" s="21" t="inlineStr"/>
+    </row>
+    <row r="321" ht="16" customHeight="1">
+      <c r="A321" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B321" s="43" t="inlineStr">
+        <is>
+          <t>NEG-ENC-03_GCM_tampered_tag</t>
+        </is>
+      </c>
+      <c r="C321" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D321" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-33</t>
+        </is>
+      </c>
+      <c r="E321" s="45" t="inlineStr"/>
+    </row>
+    <row r="322" ht="16" customHeight="1">
+      <c r="A322" s="17" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B322" s="18" t="inlineStr">
+        <is>
+          <t>NEG-ENC-04_RSA_random_ciphertext</t>
+        </is>
+      </c>
+      <c r="C322" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D322" s="19" t="inlineStr">
+        <is>
+          <t>REQ-NEG-34</t>
+        </is>
+      </c>
+      <c r="E322" s="21" t="inlineStr"/>
+    </row>
+    <row r="323" ht="16" customHeight="1">
+      <c r="A323" s="42" t="inlineStr">
+        <is>
+          <t>neg_scenarios</t>
+        </is>
+      </c>
+      <c r="B323" s="43" t="inlineStr">
+        <is>
+          <t>NEG-ENC-05_Decrypt_buffer_too_small</t>
+        </is>
+      </c>
+      <c r="C323" s="20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D323" s="44" t="inlineStr">
+        <is>
+          <t>REQ-NEG-35</t>
+        </is>
+      </c>
+      <c r="E323" s="45" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
